--- a/artfynd/A 16312-2026 artfynd.xlsx
+++ b/artfynd/A 16312-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6945448</v>
+        <v>567758</v>
       </c>
       <c r="B2" t="n">
-        <v>57280</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104232</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100084</v>
+        <v>1896</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Rödlånke</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Muscardinus avellanarius</t>
+          <t>Lythrum portula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+          <t>(L.) D. A. Webb</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lönsberg, V Fågelmara, Bl</t>
+          <t>Stångehall, Bl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555943.938039916</v>
+        <v>556058</v>
       </c>
       <c r="R2" t="n">
-        <v>6236042.040882342</v>
+        <v>6235982</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,27 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1989-04-25</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-08-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1989-04-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Fjolårsbon.</t>
+          <t>2010-08-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,19 +770,482 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Våtmark</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>hällmark</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Kjell Pettersson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Kjell Pettersson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6945448</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56614</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100084</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Hasselmus</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Muscardinus avellanarius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Lönsberg, V Fågelmara, Bl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>555944</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6236042</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Karlskrona</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Jämjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>1989-04-25</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>1989-04-25</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Fjolårsbon.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Boris Berglund</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Boris Berglund</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>65326279</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58816</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100117</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Långbensgroda</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Rana dalmatina</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Bonaparte, 1840</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>äggklumpar</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>146 Lundåkra, Bl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>555911</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6236074</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Karlskrona</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Jämjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2017-04-19</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2017-04-19</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Satellitlokal långbensgroda</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Erik Fridolf</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Erik Fridolf</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>14444</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58816</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100117</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Långbensgroda</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Rana dalmatina</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Bonaparte, 1840</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>ägg</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>147 Lundåkra, Bl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>555888</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6236036</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Karlskrona</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Jämjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2007-04-11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2007-04-11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Liten stenbrottsdamm, ca 15x20m. Omges av lövskog i NO och Ö, ganska mycket gran V om vattnet. Ett hygge med planterad lärk finns söder om vattnet. Relativt beskuggad.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Blekinge (Anly)</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Annika Lydänge</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>14443</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>146 Lundåkra, Bl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>555911</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6236074</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Karlskrona</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Jämjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2007-04-11</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2007-04-11</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gammal stenbrottsdamm. Ganska mycket salix växer längs kanterna, mest i V delen. Omges av lövskog, mest ek och bok. Litet graninslag SV om vattnet. Ett hygge med planterad lärk finns söder om vattnet.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Blekinge (Anly)</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Annika Lydänge</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16312-2026 artfynd.xlsx
+++ b/artfynd/A 16312-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/567758</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6945448</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1024,6 +1039,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65326279</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1135,6 +1155,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14444</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1246,8 +1271,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14443</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>